--- a/public/post/drafts/weekly-recap/2025Ruka/ladies_race3.xlsx
+++ b/public/post/drafts/weekly-recap/2025Ruka/ladies_race3.xlsx
@@ -629,13 +629,13 @@
         <v>51.9481518596394</v>
       </c>
       <c r="F2" t="n">
-        <v>90.4837270812224</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>9.5162729187776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -655,13 +655,13 @@
         <v>96.0445033385472</v>
       </c>
       <c r="F3" t="n">
-        <v>30.4878053362589</v>
+        <v>34.7456195189175</v>
       </c>
       <c r="G3" t="n">
         <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>64.5121946637411</v>
+        <v>60.2543804810825</v>
       </c>
     </row>
     <row r="4">
@@ -681,13 +681,13 @@
         <v>57.0049692690986</v>
       </c>
       <c r="F4" t="n">
-        <v>69.037938907864</v>
+        <v>78.6795222288461</v>
       </c>
       <c r="G4" t="n">
         <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>20.962061092136</v>
+        <v>11.3204777711539</v>
       </c>
     </row>
     <row r="5">
@@ -707,13 +707,13 @@
         <v>33.9045133160664</v>
       </c>
       <c r="F5" t="n">
-        <v>91.5568020673164</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
         <v>85</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.5568020673164</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="6">
@@ -733,13 +733,13 @@
         <v>64.6468798393266</v>
       </c>
       <c r="F6" t="n">
-        <v>62.789340501309</v>
+        <v>71.5582676693235</v>
       </c>
       <c r="G6" t="n">
         <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>17.210659498691</v>
+        <v>8.4417323306765</v>
       </c>
     </row>
     <row r="7">
@@ -759,13 +759,13 @@
         <v>71.5058235549966</v>
       </c>
       <c r="F7" t="n">
-        <v>37.3672543115808</v>
+        <v>42.5858269054448</v>
       </c>
       <c r="G7" t="n">
         <v>75</v>
       </c>
       <c r="H7" t="n">
-        <v>37.6327456884192</v>
+        <v>32.4141730945552</v>
       </c>
     </row>
     <row r="8">
@@ -785,13 +785,13 @@
         <v>66.188263158472</v>
       </c>
       <c r="F8" t="n">
-        <v>54.9703152846721</v>
+        <v>62.6472662971458</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>17.0296847153279</v>
+        <v>9.3527337028542</v>
       </c>
     </row>
     <row r="9">
@@ -811,13 +811,13 @@
         <v>124.121569279377</v>
       </c>
       <c r="F9" t="n">
-        <v>17.6321147622695</v>
+        <v>20.0945507256666</v>
       </c>
       <c r="G9" t="n">
         <v>69</v>
       </c>
       <c r="H9" t="n">
-        <v>51.3678852377305</v>
+        <v>48.9054492743334</v>
       </c>
     </row>
     <row r="10">
@@ -837,13 +837,13 @@
         <v>29.4659647962262</v>
       </c>
       <c r="F10" t="n">
-        <v>70.3339039374151</v>
+        <v>80.1564769433612</v>
       </c>
       <c r="G10" t="n">
         <v>66</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.3339039374151</v>
+        <v>-14.1564769433612</v>
       </c>
     </row>
     <row r="11">
@@ -863,13 +863,13 @@
         <v>60.4383707630141</v>
       </c>
       <c r="F11" t="n">
-        <v>53.7638382702879</v>
+        <v>61.2722971631669</v>
       </c>
       <c r="G11" t="n">
         <v>63</v>
       </c>
       <c r="H11" t="n">
-        <v>9.2361617297121</v>
+        <v>1.7277028368331</v>
       </c>
     </row>
     <row r="12">
@@ -889,13 +889,13 @@
         <v>55.5685787430825</v>
       </c>
       <c r="F12" t="n">
-        <v>49.6829000177084</v>
+        <v>56.6214301610844</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="n">
-        <v>10.3170999822916</v>
+        <v>3.3785698389156</v>
       </c>
     </row>
     <row r="13">
@@ -915,13 +915,13 @@
         <v>65.5361072788662</v>
       </c>
       <c r="F13" t="n">
-        <v>17.5953406351831</v>
+        <v>20.052640859942</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
       </c>
       <c r="H13" t="n">
-        <v>40.4046593648169</v>
+        <v>37.947359140058</v>
       </c>
     </row>
     <row r="14">
@@ -941,13 +941,13 @@
         <v>49.4628259140554</v>
       </c>
       <c r="F14" t="n">
-        <v>39.1081219858471</v>
+        <v>44.569817723272</v>
       </c>
       <c r="G14" t="n">
         <v>56</v>
       </c>
       <c r="H14" t="n">
-        <v>16.8918780141529</v>
+        <v>11.430182276728</v>
       </c>
     </row>
     <row r="15">
@@ -967,13 +967,13 @@
         <v>56.3371248310791</v>
       </c>
       <c r="F15" t="n">
-        <v>38.6398436867922</v>
+        <v>44.0361414081528</v>
       </c>
       <c r="G15" t="n">
         <v>54</v>
       </c>
       <c r="H15" t="n">
-        <v>15.3601563132078</v>
+        <v>9.9638585918472</v>
       </c>
     </row>
     <row r="16">
@@ -993,13 +993,13 @@
         <v>72.6070030994033</v>
       </c>
       <c r="F16" t="n">
-        <v>33.8421180444348</v>
+        <v>38.5683831393327</v>
       </c>
       <c r="G16" t="n">
         <v>52</v>
       </c>
       <c r="H16" t="n">
-        <v>18.1578819555652</v>
+        <v>13.4316168606673</v>
       </c>
     </row>
     <row r="17">
@@ -1019,13 +1019,13 @@
         <v>47.7486583318318</v>
       </c>
       <c r="F17" t="n">
-        <v>36.8891784056279</v>
+        <v>42.040984685869</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>13.1108215943721</v>
+        <v>7.959015314131</v>
       </c>
     </row>
     <row r="18">
@@ -1045,13 +1045,13 @@
         <v>38.9705454510849</v>
       </c>
       <c r="F18" t="n">
-        <v>8.65100859513019</v>
+        <v>9.85917647354551</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
       </c>
       <c r="H18" t="n">
-        <v>39.3489914048698</v>
+        <v>38.1408235264545</v>
       </c>
     </row>
     <row r="19">
@@ -1071,13 +1071,13 @@
         <v>48.8244282614705</v>
       </c>
       <c r="F19" t="n">
-        <v>23.0978351754783</v>
+        <v>26.3235934455202</v>
       </c>
       <c r="G19" t="n">
         <v>46</v>
       </c>
       <c r="H19" t="n">
-        <v>22.9021648245217</v>
+        <v>19.6764065544798</v>
       </c>
     </row>
     <row r="20">
@@ -1097,13 +1097,13 @@
         <v>42.3818141774766</v>
       </c>
       <c r="F20" t="n">
-        <v>30.1293024014614</v>
+        <v>34.3370493895985</v>
       </c>
       <c r="G20" t="n">
         <v>44</v>
       </c>
       <c r="H20" t="n">
-        <v>13.8706975985386</v>
+        <v>9.6629506104015</v>
       </c>
     </row>
     <row r="21">
@@ -1123,13 +1123,13 @@
         <v>-16.4085984339413</v>
       </c>
       <c r="F21" t="n">
-        <v>52.114864179351</v>
+        <v>59.3930334467949</v>
       </c>
       <c r="G21" t="n">
         <v>42</v>
       </c>
       <c r="H21" t="n">
-        <v>-10.114864179351</v>
+        <v>-17.3930334467949</v>
       </c>
     </row>
     <row r="22">
@@ -1149,13 +1149,13 @@
         <v>-10.8960917676595</v>
       </c>
       <c r="F22" t="n">
-        <v>51.4414360866402</v>
+        <v>58.6255568762576</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
       </c>
       <c r="H22" t="n">
-        <v>-11.4414360866402</v>
+        <v>-18.6255568762576</v>
       </c>
     </row>
     <row r="23">
@@ -1175,13 +1175,13 @@
         <v>54.4869606705911</v>
       </c>
       <c r="F23" t="n">
-        <v>15.5440105755742</v>
+        <v>17.714829627786</v>
       </c>
       <c r="G23" t="n">
         <v>38</v>
       </c>
       <c r="H23" t="n">
-        <v>22.4559894244258</v>
+        <v>20.285170372214</v>
       </c>
     </row>
     <row r="24">
@@ -1201,13 +1201,13 @@
         <v>-11.3507306315475</v>
       </c>
       <c r="F24" t="n">
-        <v>45.6522512520971</v>
+        <v>52.0278758898044</v>
       </c>
       <c r="G24" t="n">
         <v>36</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.6522512520971</v>
+        <v>-16.0278758898044</v>
       </c>
     </row>
     <row r="25">
@@ -1227,13 +1227,13 @@
         <v>-0.877174656133548</v>
       </c>
       <c r="F25" t="n">
-        <v>60.3271537474186</v>
+        <v>68.752221015862</v>
       </c>
       <c r="G25" t="n">
         <v>34</v>
       </c>
       <c r="H25" t="n">
-        <v>-26.3271537474186</v>
+        <v>-34.752221015862</v>
       </c>
     </row>
     <row r="26">
@@ -1253,13 +1253,13 @@
         <v>4.75642019339602</v>
       </c>
       <c r="F26" t="n">
-        <v>30.3335836477394</v>
+        <v>34.5698597995228</v>
       </c>
       <c r="G26" t="n">
         <v>32</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6664163522606</v>
+        <v>-2.5698597995228</v>
       </c>
     </row>
     <row r="27">
@@ -1279,13 +1279,13 @@
         <v>-39.9465538367754</v>
       </c>
       <c r="F27" t="n">
-        <v>61.7292788200135</v>
+        <v>70.3501616925684</v>
       </c>
       <c r="G27" t="n">
         <v>30</v>
       </c>
       <c r="H27" t="n">
-        <v>-31.7292788200135</v>
+        <v>-40.3501616925684</v>
       </c>
     </row>
     <row r="28">
@@ -1305,13 +1305,13 @@
         <v>42.5796155832347</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1625533883135</v>
+        <v>1.32491129667276</v>
       </c>
       <c r="G28" t="n">
         <v>28</v>
       </c>
       <c r="H28" t="n">
-        <v>26.8374466116865</v>
+        <v>26.6750887033272</v>
       </c>
     </row>
     <row r="29">
@@ -1331,13 +1331,13 @@
         <v>32.737955094557</v>
       </c>
       <c r="F29" t="n">
-        <v>7.95897075496758</v>
+        <v>9.07049118702584</v>
       </c>
       <c r="G29" t="n">
         <v>26</v>
       </c>
       <c r="H29" t="n">
-        <v>18.0410292450324</v>
+        <v>16.9295088129742</v>
       </c>
     </row>
     <row r="30">
@@ -1357,13 +1357,13 @@
         <v>22.8362158834227</v>
       </c>
       <c r="F30" t="n">
-        <v>6.71807842668841</v>
+        <v>7.65630042364364</v>
       </c>
       <c r="G30" t="n">
         <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>17.2819215733116</v>
+        <v>16.3436995763564</v>
       </c>
     </row>
     <row r="31">
@@ -1383,13 +1383,13 @@
         <v>-1.71606168048947</v>
       </c>
       <c r="F31" t="n">
-        <v>14.2422713182569</v>
+        <v>16.2312942782017</v>
       </c>
       <c r="G31" t="n">
         <v>22</v>
       </c>
       <c r="H31" t="n">
-        <v>7.7577286817431</v>
+        <v>5.7687057217983</v>
       </c>
     </row>
     <row r="32">
@@ -1409,13 +1409,13 @@
         <v>43.4771823051638</v>
       </c>
       <c r="F32" t="n">
-        <v>0.381970249240256</v>
+        <v>0.435314802140382</v>
       </c>
       <c r="G32" t="n">
         <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>19.6180297507597</v>
+        <v>19.5646851978596</v>
       </c>
     </row>
     <row r="33">
@@ -1435,13 +1435,13 @@
         <v>-6.22538017027387</v>
       </c>
       <c r="F33" t="n">
-        <v>24.8925963861975</v>
+        <v>28.3690043718618</v>
       </c>
       <c r="G33" t="n">
         <v>19</v>
       </c>
       <c r="H33" t="n">
-        <v>-5.8925963861975</v>
+        <v>-9.3690043718618</v>
       </c>
     </row>
     <row r="34">
@@ -1461,13 +1461,13 @@
         <v>-5.40904902990724</v>
       </c>
       <c r="F34" t="n">
-        <v>18.844343658367</v>
+        <v>21.4760750278947</v>
       </c>
       <c r="G34" t="n">
         <v>18</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.844343658366999</v>
+        <v>-3.4760750278947</v>
       </c>
     </row>
     <row r="35">
@@ -1487,13 +1487,13 @@
         <v>17.7670269865932</v>
       </c>
       <c r="F35" t="n">
-        <v>4.72459449577808</v>
+        <v>5.38441389666852</v>
       </c>
       <c r="G35" t="n">
         <v>17</v>
       </c>
       <c r="H35" t="n">
-        <v>12.2754055042219</v>
+        <v>11.6155861033315</v>
       </c>
     </row>
     <row r="36">
@@ -1513,13 +1513,13 @@
         <v>-11.2823442618892</v>
       </c>
       <c r="F36" t="n">
-        <v>5.93017470166391</v>
+        <v>6.75836097718958</v>
       </c>
       <c r="G36" t="n">
         <v>16</v>
       </c>
       <c r="H36" t="n">
-        <v>10.0698252983361</v>
+        <v>9.24163902281042</v>
       </c>
     </row>
     <row r="37">
@@ -1539,13 +1539,13 @@
         <v>-7.09906607115795</v>
       </c>
       <c r="F37" t="n">
-        <v>17.7022594737573</v>
+        <v>20.1744915882424</v>
       </c>
       <c r="G37" t="n">
         <v>15</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.7022594737573</v>
+        <v>-5.1744915882424</v>
       </c>
     </row>
     <row r="38">
@@ -1565,13 +1565,13 @@
         <v>-11.1734129385097</v>
       </c>
       <c r="F38" t="n">
-        <v>15.3228769994762</v>
+        <v>17.4628133539605</v>
       </c>
       <c r="G38" t="n">
         <v>14</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3228769994762</v>
+        <v>-3.4628133539605</v>
       </c>
     </row>
     <row r="39">
@@ -1591,13 +1591,13 @@
         <v>-14.6393207962201</v>
       </c>
       <c r="F39" t="n">
-        <v>8.19644880933393</v>
+        <v>9.34113454853053</v>
       </c>
       <c r="G39" t="n">
         <v>13</v>
       </c>
       <c r="H39" t="n">
-        <v>4.80355119066607</v>
+        <v>3.65886545146947</v>
       </c>
     </row>
     <row r="40">
@@ -1617,13 +1617,13 @@
         <v>-16.7669794729295</v>
       </c>
       <c r="F40" t="n">
-        <v>3.47220321667757</v>
+        <v>3.95711828150384</v>
       </c>
       <c r="G40" t="n">
         <v>12</v>
       </c>
       <c r="H40" t="n">
-        <v>8.52779678332243</v>
+        <v>8.04288171849616</v>
       </c>
     </row>
     <row r="41">
@@ -1643,13 +1643,13 @@
         <v>-47.9318661921936</v>
       </c>
       <c r="F41" t="n">
-        <v>24.0132267741122</v>
+        <v>27.3668252507009</v>
       </c>
       <c r="G41" t="n">
         <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>-13.0132267741122</v>
+        <v>-16.3668252507009</v>
       </c>
     </row>
     <row r="42">
@@ -1669,13 +1669,13 @@
         <v>-31.3323991317809</v>
       </c>
       <c r="F42" t="n">
-        <v>8.28697469964535</v>
+        <v>9.44430295001698</v>
       </c>
       <c r="G42" t="n">
         <v>10</v>
       </c>
       <c r="H42" t="n">
-        <v>1.71302530035465</v>
+        <v>0.555697049983021</v>
       </c>
     </row>
     <row r="43">
@@ -1695,13 +1695,13 @@
         <v>-44.1361318039953</v>
       </c>
       <c r="F43" t="n">
-        <v>3.0082669293794</v>
+        <v>3.42839036745125</v>
       </c>
       <c r="G43" t="n">
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5.9917330706206</v>
+        <v>5.57160963254875</v>
       </c>
     </row>
     <row r="44">
@@ -1743,13 +1743,13 @@
         <v>-45.0874745572562</v>
       </c>
       <c r="F45" t="n">
-        <v>8.26541967304588</v>
+        <v>9.41973762808958</v>
       </c>
       <c r="G45" t="n">
         <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.26541967304588</v>
+        <v>-2.41973762808958</v>
       </c>
     </row>
     <row r="46">
@@ -1769,13 +1769,13 @@
         <v>-54.2708411439173</v>
       </c>
       <c r="F46" t="n">
-        <v>6.66711644969363</v>
+        <v>7.59822128534349</v>
       </c>
       <c r="G46" t="n">
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.66711644969363</v>
+        <v>-1.59822128534349</v>
       </c>
     </row>
     <row r="47">
@@ -1795,13 +1795,13 @@
         <v>-66.5146554709938</v>
       </c>
       <c r="F47" t="n">
-        <v>10.7286955752136</v>
+        <v>12.2270255362503</v>
       </c>
       <c r="G47" t="n">
         <v>5</v>
       </c>
       <c r="H47" t="n">
-        <v>-5.7286955752136</v>
+        <v>-7.2270255362503</v>
       </c>
     </row>
     <row r="48">
@@ -1821,13 +1821,13 @@
         <v>-48.6399612017804</v>
       </c>
       <c r="F48" t="n">
-        <v>0.335559479997712</v>
+        <v>0.382422476441757</v>
       </c>
       <c r="G48" t="n">
         <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>3.66444052000229</v>
+        <v>3.61757752355824</v>
       </c>
     </row>
     <row r="49">
@@ -1891,13 +1891,13 @@
         <v>-71.5167417022326</v>
       </c>
       <c r="F51" t="n">
-        <v>1.15212039848492</v>
+        <v>1.31302127405451</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.15212039848492</v>
+        <v>-0.31302127405451</v>
       </c>
     </row>
     <row r="52">
@@ -1917,13 +1917,13 @@
         <v>-84.2708411439173</v>
       </c>
       <c r="F52" t="n">
-        <v>6.66711644969363</v>
+        <v>7.59822128534349</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-6.66711644969363</v>
+        <v>-7.59822128534349</v>
       </c>
     </row>
     <row r="53">
@@ -1991,13 +1991,13 @@
         <v>-71.155366529289</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.76503695470362</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>3.76503695470362</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2017,13 +2017,13 @@
         <v>-70.445847703952</v>
       </c>
       <c r="F56" t="n">
-        <v>-6.48164958909061</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>6.48164958909061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2043,13 +2043,13 @@
         <v>-67.7366037621161</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.66125332302153</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>3.66125332302153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2069,13 +2069,13 @@
         <v>-108.523602264287</v>
       </c>
       <c r="F58" t="n">
-        <v>1.14993240488253</v>
+        <v>1.31052771335443</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.14993240488253</v>
+        <v>-1.31052771335443</v>
       </c>
     </row>
     <row r="59">
@@ -2095,13 +2095,13 @@
         <v>-83.1060398527868</v>
       </c>
       <c r="F59" t="n">
-        <v>-5.76574664452997</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>5.76574664452997</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
